--- a/Excel/IngredientConfig.xlsx
+++ b/Excel/IngredientConfig.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -465,73 +465,209 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>item_gold</t>
+          <t>ingredient_carrot</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>金币材料</t>
+          <t>胡萝卜</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>vegetable</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ingredient_carrot</t>
+          <t>ingredient_mushroom</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>胡萝卜</t>
+          <t>迷雾蘑菇</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>vegetable</t>
+          <t>fungi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ingredient_meat</t>
+          <t>ingredient_lotus_root</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>肉类</t>
+          <t>莲藕</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>meat</t>
+          <t>vegetable</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ingredient_salt</t>
+          <t>ingredient_meat</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>盐</t>
+          <t>精瘦肉</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>seasoning</t>
+          <t>meat</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>ingredient_fish</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>河鲜鱼肉</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>meat</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ingredient_egg</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>鸟蛋</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ingredient_rice</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>稻米</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ingredient_wheat</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>面粉</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>grain</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ingredient_salt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>盐</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>seasoning</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ingredient_honey</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>蜂蜜</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>seasoning</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ingredient_spice</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>迷宫香料</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>seasoning</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ingredient_milk</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>牛奶</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dairy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>END</t>
         </is>
